--- a/results/Supplementary_Data_Sheet_1.xlsx
+++ b/results/Supplementary_Data_Sheet_1.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S6" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S8" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -547,10 +548,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>Table S8</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Per-policy fall probability (%) for every relief condition, side and speed under both models (policy seeds 1-8; 10 rollouts each). The mean across the eight columns equals the values in Tables 2 and 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>pp = percentage points. Kinematic and actuator measures are computed from 0.5 s to episode end or first fall; rollouts with fewer than 50 valid steps in this window are excluded from these measures (they remain in fall probability). Raw per-rollout data: results/raw/*.csv in the code repository.</t>
         </is>
@@ -571,7 +584,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -618,7 +631,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -642,7 +655,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -666,7 +679,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -690,7 +703,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -714,7 +727,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -738,7 +751,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -762,7 +775,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -786,7 +799,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -810,7 +823,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -834,7 +847,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -858,7 +871,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -882,7 +895,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -906,7 +919,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -930,7 +943,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -954,7 +967,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -978,7 +991,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -1002,7 +1015,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1026,7 +1039,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -1050,7 +1063,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -1074,7 +1087,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -1098,7 +1111,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -1122,7 +1135,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1146,7 +1159,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -1170,7 +1183,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -1194,7 +1207,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -1218,7 +1231,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -1242,7 +1255,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -1266,7 +1279,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -1290,7 +1303,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -1314,7 +1327,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -1338,7 +1351,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -1362,7 +1375,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -1386,7 +1399,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -1410,7 +1423,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -1434,7 +1447,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -1458,7 +1471,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -1482,7 +1495,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -1506,7 +1519,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
@@ -1530,7 +1543,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -1554,7 +1567,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
@@ -1578,7 +1591,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
@@ -1602,7 +1615,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
@@ -1626,7 +1639,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
@@ -1650,7 +1663,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
@@ -1674,7 +1687,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -1698,7 +1711,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
@@ -1722,7 +1735,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
@@ -1746,7 +1759,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -1770,7 +1783,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
@@ -1794,7 +1807,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
@@ -1818,7 +1831,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
@@ -1842,7 +1855,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
@@ -1866,7 +1879,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
@@ -1890,7 +1903,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
@@ -1914,7 +1927,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
@@ -1938,7 +1951,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
@@ -1962,7 +1975,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
@@ -1986,7 +1999,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
@@ -2010,7 +2023,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
@@ -2034,7 +2047,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
@@ -2058,7 +2071,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
@@ -2082,7 +2095,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
@@ -2106,7 +2119,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
@@ -2130,7 +2143,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
@@ -2154,7 +2167,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
@@ -2178,7 +2191,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
@@ -2202,7 +2215,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
@@ -2226,7 +2239,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
@@ -2250,7 +2263,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
@@ -2274,7 +2287,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
@@ -2298,7 +2311,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
@@ -2322,7 +2335,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
@@ -2346,7 +2359,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -2370,7 +2383,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -2394,7 +2407,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
@@ -2418,7 +2431,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
@@ -2442,7 +2455,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
@@ -2466,7 +2479,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
@@ -2490,7 +2503,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
@@ -2514,7 +2527,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
@@ -2538,7 +2551,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
@@ -2562,7 +2575,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
@@ -2586,7 +2599,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -2610,7 +2623,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -2634,7 +2647,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
@@ -2658,7 +2671,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
@@ -2682,7 +2695,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
@@ -2706,7 +2719,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
@@ -2730,7 +2743,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
@@ -2754,7 +2767,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
@@ -2778,7 +2791,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
@@ -2802,7 +2815,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
@@ -2826,7 +2839,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
@@ -2850,7 +2863,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -2874,7 +2887,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
@@ -2898,7 +2911,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
@@ -3690,7 +3703,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
@@ -3714,7 +3727,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
@@ -3738,7 +3751,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
@@ -3762,7 +3775,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
@@ -3786,7 +3799,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
@@ -3810,7 +3823,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
@@ -3834,7 +3847,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
@@ -3858,7 +3871,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
@@ -3882,7 +3895,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
@@ -3906,7 +3919,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
@@ -3930,7 +3943,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
@@ -3954,7 +3967,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
@@ -3978,7 +3991,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
@@ -4002,7 +4015,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
@@ -4026,7 +4039,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
@@ -4050,7 +4063,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
@@ -4074,7 +4087,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
@@ -4098,7 +4111,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
@@ -4122,7 +4135,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
@@ -4146,7 +4159,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
@@ -4170,7 +4183,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
@@ -4194,7 +4207,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
@@ -4218,7 +4231,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
@@ -4242,7 +4255,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
@@ -4266,7 +4279,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
@@ -4290,7 +4303,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
@@ -4314,7 +4327,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
@@ -4338,7 +4351,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
@@ -4362,7 +4375,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
@@ -4386,7 +4399,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
@@ -4410,7 +4423,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
@@ -4434,7 +4447,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>ankle_pitch</t>
+          <t>ankle pitch</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
@@ -4458,7 +4471,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
@@ -4482,7 +4495,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
@@ -4506,7 +4519,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
@@ -4530,7 +4543,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
@@ -4554,7 +4567,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
@@ -4578,7 +4591,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
@@ -4602,7 +4615,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
@@ -4626,7 +4639,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
@@ -4650,7 +4663,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
@@ -4674,7 +4687,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
@@ -4698,7 +4711,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
@@ -4722,7 +4735,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
@@ -4746,7 +4759,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
@@ -4770,7 +4783,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
@@ -4794,7 +4807,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
@@ -4818,7 +4831,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
@@ -4842,7 +4855,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
@@ -4866,7 +4879,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
@@ -4890,7 +4903,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
@@ -4914,7 +4927,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
@@ -4938,7 +4951,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
@@ -4962,7 +4975,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
@@ -4986,7 +4999,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
@@ -5010,7 +5023,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
@@ -5034,7 +5047,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
@@ -5058,7 +5071,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
@@ -5082,7 +5095,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
@@ -5106,7 +5119,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C189" s="2" t="n">
@@ -5130,7 +5143,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
@@ -5154,7 +5167,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
@@ -5178,7 +5191,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C192" s="2" t="n">
@@ -5202,7 +5215,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>equinovarus</t>
+          <t>ankle pitch + roll</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
@@ -5226,7 +5239,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C194" s="2" t="n">
@@ -5250,7 +5263,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C195" s="2" t="n">
@@ -5274,7 +5287,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C196" s="2" t="n">
@@ -5298,7 +5311,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C197" s="2" t="n">
@@ -5322,7 +5335,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C198" s="2" t="n">
@@ -5346,7 +5359,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C199" s="2" t="n">
@@ -5370,7 +5383,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C200" s="2" t="n">
@@ -5394,7 +5407,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C201" s="2" t="n">
@@ -5418,7 +5431,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
@@ -5442,7 +5455,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C203" s="2" t="n">
@@ -5466,7 +5479,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C204" s="2" t="n">
@@ -5490,7 +5503,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C205" s="2" t="n">
@@ -5514,7 +5527,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C206" s="2" t="n">
@@ -5538,7 +5551,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C207" s="2" t="n">
@@ -5562,7 +5575,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C208" s="2" t="n">
@@ -5586,7 +5599,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C209" s="2" t="n">
@@ -5610,7 +5623,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C210" s="2" t="n">
@@ -5634,7 +5647,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C211" s="2" t="n">
@@ -5658,7 +5671,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C212" s="2" t="n">
@@ -5682,7 +5695,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C213" s="2" t="n">
@@ -5706,7 +5719,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C214" s="2" t="n">
@@ -5730,7 +5743,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C215" s="2" t="n">
@@ -5754,7 +5767,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C216" s="2" t="n">
@@ -5778,7 +5791,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C217" s="2" t="n">
@@ -5802,7 +5815,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C218" s="2" t="n">
@@ -5826,7 +5839,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C219" s="2" t="n">
@@ -5850,7 +5863,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C220" s="2" t="n">
@@ -5874,7 +5887,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C221" s="2" t="n">
@@ -5898,7 +5911,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C222" s="2" t="n">
@@ -5922,7 +5935,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C223" s="2" t="n">
@@ -5946,7 +5959,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C224" s="2" t="n">
@@ -5970,7 +5983,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>hip_pitch</t>
+          <t>hip pitch</t>
         </is>
       </c>
       <c r="C225" s="2" t="n">
@@ -43407,4 +43420,5726 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L129"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>relief condition</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>speed (m/s)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>policy seed 1 (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>policy seed 2 (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>policy seed 3 (%)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>policy seed 4 (%)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>policy seed 5 (%)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>policy seed 6 (%)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>policy seed 7 (%)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>policy seed 8 (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Untreated</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Untreated</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Untreated</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Untreated</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Knee</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Knee</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Knee</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Knee</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Ankle</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Ankle</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Ankle</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Ankle</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Hip + knee</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Hip + knee</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Hip + knee</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Hip + knee</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Hip + ankle</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Hip + ankle</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Hip + ankle</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Hip + ankle</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Knee + ankle</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Knee + ankle</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Knee + ankle</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Knee + ankle</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>All three (reference)</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>All three (reference)</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>All three (reference)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>All three (reference)</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Untreated</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Untreated</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Untreated</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Untreated</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Knee</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Knee</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Knee</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Knee</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Ankle</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Ankle</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Ankle</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Ankle</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Hip + knee</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Hip + knee</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Hip + knee</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Hip + knee</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Hip + ankle</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Hip + ankle</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Hip + ankle</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Hip + ankle</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Knee + ankle</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Knee + ankle</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Knee + ankle</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Knee + ankle</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>All three (reference)</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>All three (reference)</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>All three (reference)</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>contracture-like (damping x10,000)</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>All three (reference)</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Untreated</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Untreated</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Untreated</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Untreated</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Knee</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Knee</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Knee</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Knee</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Ankle</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Ankle</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Ankle</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Ankle</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Hip + knee</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Hip + knee</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Hip + knee</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Hip + knee</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Hip + ankle</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Hip + ankle</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Hip + ankle</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Hip + ankle</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Knee + ankle</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Knee + ankle</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Knee + ankle</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Knee + ankle</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>All three (reference)</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>All three (reference)</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>All three (reference)</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>All three (reference)</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Untreated</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Untreated</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Untreated</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Untreated</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Hip</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Knee</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Knee</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Knee</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Knee</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Ankle</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Ankle</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Ankle</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Ankle</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Hip + knee</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Hip + knee</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Hip + knee</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Hip + knee</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Hip + ankle</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Hip + ankle</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Hip + ankle</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Hip + ankle</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Knee + ankle</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Knee + ankle</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Knee + ankle</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Knee + ankle</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>All three (reference)</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>All three (reference)</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>All three (reference)</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>direction-selective (right b = 40, left b = 50)</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>All three (reference)</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>